--- a/input/mapping/032. OCB_GOLD_TCKH_V_TB_AR_DTL_PHAT.xlsx
+++ b/input/mapping/032. OCB_GOLD_TCKH_V_TB_AR_DTL_PHAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OCB\Zone_C\Code dev lại silver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="13_ncr:1_{18B2E4A2-A6C2-47DA-A270-A9F713991D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECA69271-E276-41C8-B90C-173B844A3364}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{18B2E4A2-A6C2-47DA-A270-A9F713991D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BFE2996-19D2-44F9-9ECD-F2ABF09096B1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="7" r:id="rId1"/>
@@ -1285,9 +1285,14 @@
 WHERE Z3.CDR_DT_ID &gt;= 20240701;</t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE holiday AS
+INSERT OVERWRITE holiday (
+    DATA_DATE_DT,
+    HOLIDAY_DATE_DT,
+    DATA_DT,
+    HOLIDAY_DT
+)
 SELECT
     TO_DATE(CAST(MAX(W.msr_prd_id) AS STRING), 'yyyyMMdd')   AS DATA_DATE_DT,
     TO_DATE(CAST(D.msr_prd_id AS STRING), 'yyyyMMdd')        AS HOLIDAY_DATE_DT,
@@ -1298,12 +1303,21 @@
     ON  D.msr_prd_id &gt; W.msr_prd_id
     AND W.bsn_day_f = 1
 WHERE D.bsn_day_f = 0
-GROUP BY D.msr_prd_id;</t>
+GROUP BY D.msr_prd_id;
+</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE working_day AS
+INSERT OVERWRITE working_day (
+    DATA_DT,
+    FROM_DATE_DT,
+    FROM_DT,
+    END_DT,
+    END_DATE_DT,
+    BEGIN_OF_MONTH,
+    BEGIN_OF_MONTH_DATE
+)
 WITH
 v_from_dt AS (
     SELECT
@@ -1387,28 +1401,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -1416,15 +1411,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -1433,7 +1425,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -1444,18 +1435,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -1466,15 +1462,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -1504,9 +1495,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -1515,8 +1505,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -1525,10 +1515,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -1537,9 +1527,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -1573,8 +1579,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>V_TB_AR_DTL
@@ -3772,7 +3777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4083,36 +4088,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4146,6 +4154,7 @@
     <xf numFmtId="0" fontId="27" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4511,536 +4520,536 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:21" ht="6" customHeight="1"/>
     <row r="3" spans="1:21" ht="22.15" customHeight="1">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="G3" s="117" t="s">
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="G3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="L3" s="118" t="s">
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="L3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="118"/>
-      <c r="N3" s="118"/>
-      <c r="O3" s="118"/>
-      <c r="Q3" s="119" t="s">
+      <c r="M3" s="117"/>
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
+      <c r="Q3" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="119"/>
+      <c r="R3" s="118"/>
+      <c r="S3" s="118"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="G4" s="120" t="s">
+      <c r="C4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="G4" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120"/>
-      <c r="L4" s="121" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
-      <c r="Q4" s="122" t="s">
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="L4" s="120" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120"/>
+      <c r="Q4" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="122"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="121"/>
+      <c r="T4" s="121"/>
     </row>
     <row r="5" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-      <c r="O5" s="121"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
       <c r="P5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q5" s="122"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122"/>
-      <c r="T5" s="122"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="121"/>
+      <c r="S5" s="121"/>
+      <c r="T5" s="121"/>
     </row>
     <row r="6" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="120"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="121"/>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="120"/>
+      <c r="N6" s="120"/>
+      <c r="O6" s="120"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="121"/>
+      <c r="S6" s="121"/>
+      <c r="T6" s="121"/>
     </row>
     <row r="7" spans="1:21" ht="7.15" customHeight="1">
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="120"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="121"/>
-      <c r="N7" s="121"/>
-      <c r="O7" s="121"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="120"/>
+      <c r="O7" s="120"/>
     </row>
     <row r="8" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="120"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="121"/>
-      <c r="N8" s="121"/>
-      <c r="O8" s="121"/>
-      <c r="Q8" s="122" t="s">
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
+      <c r="L8" s="120"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="120"/>
+      <c r="Q8" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="R8" s="122"/>
-      <c r="S8" s="122"/>
-      <c r="T8" s="122"/>
+      <c r="R8" s="121"/>
+      <c r="S8" s="121"/>
+      <c r="T8" s="121"/>
     </row>
     <row r="9" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="120"/>
+      <c r="O9" s="120"/>
       <c r="P9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="122"/>
-      <c r="S9" s="122"/>
-      <c r="T9" s="122"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="121"/>
+      <c r="T9" s="121"/>
     </row>
     <row r="10" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="120"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="121"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="121"/>
-      <c r="Q10" s="122"/>
-      <c r="R10" s="122"/>
-      <c r="S10" s="122"/>
-      <c r="T10" s="122"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="120"/>
+      <c r="Q10" s="121"/>
+      <c r="R10" s="121"/>
+      <c r="S10" s="121"/>
+      <c r="T10" s="121"/>
     </row>
     <row r="11" spans="1:21" ht="7.15" customHeight="1">
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="120"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="121"/>
-      <c r="O11" s="121"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="120"/>
+      <c r="O11" s="120"/>
     </row>
     <row r="12" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B12" s="120"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="120"/>
-      <c r="J12" s="120"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="121"/>
-      <c r="Q12" s="123" t="s">
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="120"/>
+      <c r="Q12" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="R12" s="123"/>
-      <c r="S12" s="123"/>
-      <c r="T12" s="123"/>
+      <c r="R12" s="122"/>
+      <c r="S12" s="122"/>
+      <c r="T12" s="122"/>
     </row>
     <row r="13" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B13" s="120"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="119"/>
       <c r="F13" s="10"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="120"/>
-      <c r="J13" s="120"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="119"/>
+      <c r="J13" s="119"/>
       <c r="K13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
       <c r="P13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="123"/>
-      <c r="S13" s="123"/>
-      <c r="T13" s="123"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="122"/>
+      <c r="S13" s="122"/>
+      <c r="T13" s="122"/>
     </row>
     <row r="14" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="120"/>
-      <c r="J14" s="120"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="123"/>
-      <c r="S14" s="123"/>
-      <c r="T14" s="123"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="119"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="120"/>
+      <c r="Q14" s="122"/>
+      <c r="R14" s="122"/>
+      <c r="S14" s="122"/>
+      <c r="T14" s="122"/>
     </row>
     <row r="15" spans="1:21" ht="7.15" customHeight="1">
-      <c r="B15" s="120"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="120"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="119"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="120"/>
+      <c r="N15" s="120"/>
+      <c r="O15" s="120"/>
     </row>
     <row r="16" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="121"/>
-      <c r="N16" s="121"/>
-      <c r="O16" s="121"/>
-      <c r="Q16" s="122" t="s">
+      <c r="B16" s="119"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="Q16" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="R16" s="122"/>
-      <c r="S16" s="122"/>
-      <c r="T16" s="122"/>
+      <c r="R16" s="121"/>
+      <c r="S16" s="121"/>
+      <c r="T16" s="121"/>
     </row>
     <row r="17" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B17" s="120"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
       <c r="F17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="119"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="120"/>
       <c r="P17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q17" s="122"/>
-      <c r="R17" s="122"/>
-      <c r="S17" s="122"/>
-      <c r="T17" s="122"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="121"/>
+      <c r="S17" s="121"/>
+      <c r="T17" s="121"/>
     </row>
     <row r="18" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B18" s="120"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="120"/>
-      <c r="E18" s="120"/>
-      <c r="G18" s="120"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120"/>
-      <c r="J18" s="120"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="121"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="122"/>
-      <c r="S18" s="122"/>
-      <c r="T18" s="122"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="119"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="121"/>
+      <c r="S18" s="121"/>
+      <c r="T18" s="121"/>
     </row>
     <row r="19" spans="2:20" ht="10.15" customHeight="1">
-      <c r="B19" s="120"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="121"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="120"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
     </row>
     <row r="20" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B20" s="120"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="120"/>
-      <c r="L20" s="121"/>
-      <c r="M20" s="121"/>
-      <c r="N20" s="121"/>
-      <c r="O20" s="121"/>
-      <c r="Q20" s="123" t="s">
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="120"/>
+      <c r="Q20" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="R20" s="123"/>
-      <c r="S20" s="123"/>
-      <c r="T20" s="123"/>
+      <c r="R20" s="122"/>
+      <c r="S20" s="122"/>
+      <c r="T20" s="122"/>
     </row>
     <row r="21" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B21" s="120"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
-      <c r="G21" s="120"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="120"/>
-      <c r="J21" s="120"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="121"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="121"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="120"/>
+      <c r="O21" s="120"/>
       <c r="P21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="123"/>
-      <c r="S21" s="123"/>
-      <c r="T21" s="123"/>
+      <c r="Q21" s="122"/>
+      <c r="R21" s="122"/>
+      <c r="S21" s="122"/>
+      <c r="T21" s="122"/>
     </row>
     <row r="22" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B22" s="120"/>
-      <c r="C22" s="120"/>
-      <c r="D22" s="120"/>
-      <c r="E22" s="120"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="120"/>
-      <c r="J22" s="120"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="121"/>
-      <c r="N22" s="121"/>
-      <c r="O22" s="121"/>
-      <c r="Q22" s="123"/>
-      <c r="R22" s="123"/>
-      <c r="S22" s="123"/>
-      <c r="T22" s="123"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="120"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="120"/>
+      <c r="Q22" s="122"/>
+      <c r="R22" s="122"/>
+      <c r="S22" s="122"/>
+      <c r="T22" s="122"/>
     </row>
     <row r="23" spans="2:20" ht="7.9" customHeight="1">
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="120"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
     </row>
     <row r="24" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B24" s="120"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="120"/>
-      <c r="E24" s="120"/>
-      <c r="G24" s="120"/>
-      <c r="H24" s="120"/>
-      <c r="I24" s="120"/>
-      <c r="J24" s="120"/>
-      <c r="L24" s="122" t="s">
+      <c r="B24" s="119"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="L24" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="M24" s="122"/>
-      <c r="N24" s="122"/>
-      <c r="O24" s="122"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="121"/>
     </row>
     <row r="25" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B25" s="120"/>
-      <c r="C25" s="120"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="120"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="120"/>
-      <c r="J25" s="120"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
       <c r="K25" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="122"/>
-      <c r="M25" s="122"/>
-      <c r="N25" s="122"/>
-      <c r="O25" s="122"/>
+      <c r="L25" s="121"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="121"/>
     </row>
     <row r="26" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B26" s="120"/>
-      <c r="C26" s="120"/>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="120"/>
-      <c r="J26" s="120"/>
-      <c r="L26" s="122"/>
-      <c r="M26" s="122"/>
-      <c r="N26" s="122"/>
-      <c r="O26" s="122"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
     </row>
     <row r="27" spans="2:20" ht="15" customHeight="1">
-      <c r="B27" s="120"/>
-      <c r="C27" s="120"/>
-      <c r="D27" s="120"/>
-      <c r="E27" s="120"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="120"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
     </row>
     <row r="28" spans="2:20" ht="7.9" customHeight="1">
-      <c r="B28" s="120"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="120"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="120"/>
-      <c r="J28" s="120"/>
-      <c r="L28" s="122" t="s">
+      <c r="B28" s="119"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="119"/>
+      <c r="J28" s="119"/>
+      <c r="L28" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="M28" s="122"/>
-      <c r="N28" s="122"/>
-      <c r="O28" s="122"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="121"/>
     </row>
     <row r="29" spans="2:20" ht="22.15" customHeight="1">
-      <c r="B29" s="120"/>
-      <c r="C29" s="120"/>
-      <c r="D29" s="120"/>
-      <c r="E29" s="120"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
       <c r="F29" s="10"/>
-      <c r="G29" s="120"/>
-      <c r="H29" s="120"/>
-      <c r="I29" s="120"/>
-      <c r="J29" s="120"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="119"/>
       <c r="K29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="122"/>
-      <c r="M29" s="122"/>
-      <c r="N29" s="122"/>
-      <c r="O29" s="122"/>
+      <c r="L29" s="121"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="121"/>
     </row>
     <row r="30" spans="2:20" ht="22.15" customHeight="1">
-      <c r="B30" s="120"/>
-      <c r="C30" s="120"/>
-      <c r="D30" s="120"/>
-      <c r="E30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="120"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="120"/>
-      <c r="L30" s="122"/>
-      <c r="M30" s="122"/>
-      <c r="N30" s="122"/>
-      <c r="O30" s="122"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="119"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
     </row>
     <row r="31" spans="2:20" ht="18" customHeight="1"/>
     <row r="32" spans="2:20" ht="18" customHeight="1"/>
@@ -5053,31 +5062,31 @@
     </row>
     <row r="35" spans="7:8" ht="29.25" customHeight="1">
       <c r="G35" s="13"/>
-      <c r="H35" s="135" t="s">
+      <c r="H35" s="137" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="7:8" ht="23.25" customHeight="1">
       <c r="G36" s="14"/>
-      <c r="H36" s="135" t="s">
+      <c r="H36" s="137" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="37" spans="7:8" ht="25.5" customHeight="1">
       <c r="G37" s="15"/>
-      <c r="H37" s="135" t="s">
+      <c r="H37" s="137" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="38" spans="7:8" ht="25.15" customHeight="1">
       <c r="G38" s="16"/>
-      <c r="H38" s="135" t="s">
+      <c r="H38" s="137" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="39" spans="7:8" ht="25.15" customHeight="1">
       <c r="G39" s="17"/>
-      <c r="H39" s="135" t="s">
+      <c r="H39" s="137" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5175,7 +5184,7 @@
       <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="114" t="s">
         <v>29</v>
       </c>
     </row>
@@ -5219,7 +5228,7 @@
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="136" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5230,7 +5239,7 @@
       <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="114" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5275,13 +5284,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="40.5" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
     </row>
     <row r="2" spans="1:5" ht="19.899999999999999" customHeight="1">
       <c r="A2" s="98" t="s">
@@ -5340,13 +5349,13 @@
       <c r="E5" s="103"/>
     </row>
     <row r="6" spans="1:5" ht="23.25" customHeight="1">
-      <c r="A6" s="114" t="s">
+      <c r="A6" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
     </row>
     <row r="7" spans="1:5" ht="57.75" customHeight="1">
       <c r="A7" s="98" t="s">
@@ -6603,13 +6612,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="38.25" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="125" t="s">
         <v>221</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
     </row>
     <row r="2" spans="1:5" ht="19.899999999999999" customHeight="1">
       <c r="A2" s="104" t="s">
@@ -6694,20 +6703,20 @@
       <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="6" customHeight="1">
-      <c r="A8" s="136"/>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
     </row>
     <row r="9" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="125" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
     </row>
     <row r="10" spans="1:5" ht="26.45" customHeight="1">
       <c r="A10" s="104" t="s">
@@ -7942,22 +7951,22 @@
       <c r="E91" s="106"/>
     </row>
     <row r="93" spans="1:5" ht="18.75">
-      <c r="A93" s="124" t="s">
+      <c r="A93" s="125" t="s">
         <v>238</v>
       </c>
-      <c r="B93" s="125"/>
-      <c r="C93" s="125"/>
-      <c r="D93" s="125"/>
-      <c r="E93" s="125"/>
+      <c r="B93" s="126"/>
+      <c r="C93" s="126"/>
+      <c r="D93" s="126"/>
+      <c r="E93" s="126"/>
     </row>
     <row r="95" spans="1:5" ht="48.75" customHeight="1">
-      <c r="A95" s="124" t="s">
+      <c r="A95" s="125" t="s">
         <v>221</v>
       </c>
-      <c r="B95" s="125"/>
-      <c r="C95" s="125"/>
-      <c r="D95" s="125"/>
-      <c r="E95" s="125"/>
+      <c r="B95" s="126"/>
+      <c r="C95" s="126"/>
+      <c r="D95" s="126"/>
+      <c r="E95" s="126"/>
     </row>
     <row r="96" spans="1:5" ht="18.75">
       <c r="A96" s="104" t="s">
@@ -8042,20 +8051,20 @@
       <c r="E101" s="8"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="136"/>
-      <c r="B102" s="136"/>
-      <c r="C102" s="136"/>
-      <c r="D102" s="136"/>
-      <c r="E102" s="136"/>
+      <c r="A102" s="138"/>
+      <c r="B102" s="138"/>
+      <c r="C102" s="138"/>
+      <c r="D102" s="138"/>
+      <c r="E102" s="138"/>
     </row>
     <row r="103" spans="1:5" ht="18.75">
-      <c r="A103" s="124" t="s">
+      <c r="A103" s="125" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="125"/>
-      <c r="C103" s="125"/>
-      <c r="D103" s="125"/>
-      <c r="E103" s="125"/>
+      <c r="B103" s="126"/>
+      <c r="C103" s="126"/>
+      <c r="D103" s="126"/>
+      <c r="E103" s="126"/>
     </row>
     <row r="104" spans="1:5" ht="37.5">
       <c r="A104" s="104" t="s">
@@ -9290,22 +9299,22 @@
       <c r="E185" s="106"/>
     </row>
     <row r="187" spans="1:5" ht="18.75">
-      <c r="A187" s="124" t="s">
+      <c r="A187" s="125" t="s">
         <v>238</v>
       </c>
-      <c r="B187" s="125"/>
-      <c r="C187" s="125"/>
-      <c r="D187" s="125"/>
-      <c r="E187" s="125"/>
+      <c r="B187" s="126"/>
+      <c r="C187" s="126"/>
+      <c r="D187" s="126"/>
+      <c r="E187" s="126"/>
     </row>
     <row r="189" spans="1:5" ht="48.75" customHeight="1">
-      <c r="A189" s="124" t="s">
+      <c r="A189" s="125" t="s">
         <v>221</v>
       </c>
-      <c r="B189" s="125"/>
-      <c r="C189" s="125"/>
-      <c r="D189" s="125"/>
-      <c r="E189" s="125"/>
+      <c r="B189" s="126"/>
+      <c r="C189" s="126"/>
+      <c r="D189" s="126"/>
+      <c r="E189" s="126"/>
     </row>
     <row r="190" spans="1:5" ht="18.75">
       <c r="A190" s="104" t="s">
@@ -9365,18 +9374,18 @@
       <c r="D193" s="7"/>
     </row>
     <row r="194" spans="1:4">
-      <c r="A194" s="136"/>
-      <c r="B194" s="136"/>
-      <c r="C194" s="136"/>
-      <c r="D194" s="136"/>
+      <c r="A194" s="138"/>
+      <c r="B194" s="138"/>
+      <c r="C194" s="138"/>
+      <c r="D194" s="138"/>
     </row>
     <row r="195" spans="1:4" ht="18.75">
-      <c r="A195" s="124" t="s">
+      <c r="A195" s="125" t="s">
         <v>229</v>
       </c>
-      <c r="B195" s="125"/>
-      <c r="C195" s="125"/>
-      <c r="D195" s="125"/>
+      <c r="B195" s="126"/>
+      <c r="C195" s="126"/>
+      <c r="D195" s="126"/>
     </row>
     <row r="196" spans="1:4" ht="37.5">
       <c r="A196" s="104" t="s">
@@ -10557,13 +10566,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="127" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
       <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6">
@@ -10612,13 +10621,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="128" t="s">
         <v>363</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
+      <c r="B5" s="128"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
       <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6">
@@ -10746,13 +10755,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="131" t="s">
         <v>375</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="132"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133"/>
       <c r="F1" s="23"/>
       <c r="G1" s="24"/>
     </row>
@@ -10964,14 +10973,14 @@
       <c r="G12" s="39"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
-      <c r="A13" s="128" t="s">
+      <c r="A13" s="129" t="s">
         <v>408</v>
       </c>
-      <c r="B13" s="128"/>
-      <c r="C13" s="128"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="129"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="130"/>
       <c r="G13" s="41"/>
     </row>
     <row r="14" spans="1:7" ht="27">
@@ -11333,13 +11342,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34.5" customHeight="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="134" t="s">
         <v>448</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
     </row>
     <row r="2" spans="1:5" ht="27" customHeight="1">
       <c r="A2" s="64" t="s">
@@ -11409,13 +11418,13 @@
       <c r="E6" s="73"/>
     </row>
     <row r="7" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="134" t="s">
         <v>454</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1">
       <c r="A8" s="64" t="s">
@@ -11525,13 +11534,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="134" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
     </row>
     <row r="2" spans="1:5" ht="23.25" customHeight="1">
       <c r="A2" s="64" t="s">
@@ -11611,13 +11620,13 @@
       <c r="E6" s="73"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="134" t="s">
         <v>478</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
+      <c r="E7" s="135"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="64" t="s">
@@ -11765,6 +11774,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -11936,33 +11964,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36234F88-639F-4C47-9D16-0EF667429B42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BB095A-83D2-42D5-81BA-77562D80BA51}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73BB095A-83D2-42D5-81BA-77562D80BA51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE3BB95-791F-41EC-B525-169D350DCC54}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE3BB95-791F-41EC-B525-169D350DCC54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36234F88-639F-4C47-9D16-0EF667429B42}"/>
 </file>